--- a/LCFT_Site_Directory.xlsx
+++ b/LCFT_Site_Directory.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Jack Dixon</t>
+          <t>Martin Turner</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Michael Ashworth</t>
+          <t>Usman Danbibi</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
